--- a/benchmark/generated_files/RIC-3_V_042.xlsx
+++ b/benchmark/generated_files/RIC-3_V_042.xlsx
@@ -462,15 +462,15 @@
         <v>46024</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 25,22 EUR DEL 02.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 25,85 EUR DEL 02.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-25.22</v>
+        <v>-25.85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -480,18 +480,18 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,84 EUR DEL 02.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9466 PITTAROSSO MESTRE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-12.84</v>
+        <v>-128.63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,11 +508,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 82,97 EUR DEL 03.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Bonif. v/fav. - RIF:215234327 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-82.97</v>
+        <v>232.56</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -529,11 +529,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8176 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 245,33 EUR DEL 04.01.2026 A (ITA) OTTICA AVANZI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-155.24</v>
+        <v>-245.33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -550,11 +550,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3663 DM</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-30.89</v>
+        <v>-87.86</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -564,18 +564,18 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213630643 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Pagam. POS - PAGAMENTO POS 133,79 EUR DEL 06.01.2026 A (ITA) CENTRO MEDICO SANTAGOSTINO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>250.4</v>
+        <v>-133.79</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,18 +585,18 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46034</v>
+        <v>46028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,39 EUR DEL 10.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 177,55 EUR DEL 06.01.2026 A (ITA) SALMOIRAGHI &amp; VIGANÒ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-96.39</v>
+        <v>-177.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -606,18 +606,18 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 60,09 EUR DEL 10.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 23,17 EUR DEL 06.01.2026 A (ITA) FLOWER BURGER BERGAMO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-60.09</v>
+        <v>-23.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -627,18 +627,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216769570 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Bonif. v/fav. - RIF:211478777 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>286.99</v>
+        <v>230.27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -648,18 +648,18 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 9,72 EUR DEL 08.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-41.34</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -669,18 +669,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>46036</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,36 EUR DEL 13.01.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 120,34 EUR DEL 12.01.2026 A (ITA) OTTICA AVANZI</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-13.36</v>
+        <v>-120.34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -690,18 +690,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,03 EUR DEL 13.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1076 KEBHOUZE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-69.03</v>
+        <v>-28.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -711,18 +711,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 99,49 EUR DEL 16.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 147,85 EUR DEL 14.01.2026 A (ITA) CALZEDONIA GROUP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-99.48999999999999</v>
+        <v>-147.85</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -732,18 +732,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46043</v>
+        <v>46037</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 90,27 EUR DEL 19.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6579 SNIPES ROZZANO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-90.27</v>
+        <v>-21.07</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -753,18 +753,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46044</v>
+        <v>46039</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 102,83 EUR DEL 20.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9857 VALMANO PORTA NUOVA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-102.83</v>
+        <v>-34.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -774,18 +774,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46043</v>
+        <v>46038</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2697 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 92,35 EUR DEL 16.01.2026 A (ITA) FARMACIA DR ROSSI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-74.29000000000001</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -795,18 +795,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46044</v>
+        <v>46040</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 60,10 EUR DEL 22.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4763 LAFARMACIA. BARI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-60.1</v>
+        <v>-157.02</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -816,18 +816,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46045</v>
+        <v>46042</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 66,16 EUR DEL 23.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 98,65 EUR DEL 18.01.2026 A (ITA) NATURA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-66.16</v>
+        <v>-98.65000000000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -837,18 +837,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 78,08 EUR DEL 23.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Bonif. v/fav. - RIF:216297521 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-78.08</v>
+        <v>50.51</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -858,18 +858,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46046</v>
+        <v>46041</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46046</v>
+        <v>46041</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:219341418 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 125,47 EUR DEL 19.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-57.47</v>
+        <v>-125.47</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -879,18 +879,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46046</v>
+        <v>46043</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46047</v>
+        <v>46043</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213237572 ORD. RICARICA REVOLUT LAURA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9708 CONAD CITY NORD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>251.15</v>
+        <v>-127.87</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -900,18 +900,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46047</v>
+        <v>46044</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46047</v>
+        <v>46044</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 53,21 EUR DEL 25.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 127,46 EUR DEL 22.01.2026 A (ITA) DECÒ</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-53.21</v>
+        <v>-127.46</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -921,18 +921,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46048</v>
+        <v>46045</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 45,71 EUR DEL 22.01.2026 A (ITA) PITAYA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-7.8</v>
+        <v>-45.71</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -942,18 +942,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46050</v>
+        <v>46045</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46050</v>
+        <v>46045</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7908 LIDL ITALIA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-13.73</v>
+        <v>-179.05</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -963,18 +963,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46050</v>
+        <v>46045</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46050</v>
+        <v>46046</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213291298 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>142.42</v>
+        <v>-6.15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -984,18 +984,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46053</v>
+        <v>46046</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 105,95 EUR DEL 30.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>Bonif. v/fav. - RIF:213321740 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-105.95</v>
+        <v>168.71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1005,18 +1005,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46053</v>
+        <v>46046</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46053</v>
+        <v>46047</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9727 MIX MARKT</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-65.95</v>
+        <v>-147.12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46053</v>
+        <v>46047</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46053</v>
+        <v>46048</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218054553 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,24 EUR DEL 25.01.2026 A (ITA) THUN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>108.12</v>
+        <v>-71.23999999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1047,18 +1047,18 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46055</v>
+        <v>46047</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46055</v>
+        <v>46047</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 221,19 EUR DEL 02.02.2026 A (ITA) CENTRO MEDICO SANTAGOSTINO</t>
+          <t>Bonif. v/fav. - RIF:214593503 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-221.19</v>
+        <v>257.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1068,18 +1068,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46056</v>
+        <v>46049</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46056</v>
+        <v>46049</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 35,86 EUR DEL 03.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 50,88 EUR DEL 27.01.2026 A (ITA) IKEA BISTRO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-35.86</v>
+        <v>-50.88</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1089,18 +1089,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 42,16 EUR DEL 27.01.2026 A (ITA) CHURCH'S VENEZIA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-13.08</v>
+        <v>-42.16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1110,18 +1110,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 134,50 EUR DEL 04.02.2026 A (ITA) OTTICA AVANZI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7453 GABOR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-134.5</v>
+        <v>-96.45</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1131,18 +1131,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 161,98 EUR DEL 05.02.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5688 IKEA BISTRO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-161.98</v>
+        <v>-54.74</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1152,18 +1152,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46059</v>
+        <v>46051</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-28.45</v>
+        <v>-13.36</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1173,18 +1173,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46060</v>
+        <v>46054</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-217133034</t>
+          <t>Pagam. POS - PAGAMENTO POS 67,16 EUR DEL 30.01.2026 A (ITA) ZARA ITALIA SRL</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-11.9</v>
+        <v>-67.16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1194,18 +1194,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46060</v>
+        <v>46052</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 65,32 EUR DEL 06.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 30,65 EUR DEL 30.01.2026 A (ITA) PETMARK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-65.31999999999999</v>
+        <v>-30.65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1215,18 +1215,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46060</v>
+        <v>46056</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46060</v>
+        <v>46056</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Bonif. v/fav. - RIF:216381032 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-19.73</v>
+        <v>61.12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1236,18 +1236,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 114,62 EUR DEL 07.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 72,22 EUR DEL 04.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-114.62</v>
+        <v>-72.22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1257,18 +1257,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46061</v>
+        <v>46057</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46061</v>
+        <v>46057</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 6,96 EUR DEL 08.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 64,25 EUR DEL 04.02.2026 A (ITA) HISTOIRE D'OR</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-6.96</v>
+        <v>-64.25</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1278,18 +1278,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46062</v>
+        <v>46060</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217274282 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Pagam. POS - PAGAMENTO POS 9,87 EUR DEL 05.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>159.24</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1299,18 +1299,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46063</v>
+        <v>46060</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46063</v>
+        <v>46061</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 89,49 EUR DEL 10.02.2026 A (ITA) CENTRO MEDICO SANTAGOSTINO</t>
+          <t>Bonif. v/fav. - RIF:212869830 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-89.48999999999999</v>
+        <v>59.43</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1320,18 +1320,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46065</v>
+        <v>46062</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 61,23 EUR DEL 11.02.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
+          <t>Pagam. POS - PAGAMENTO POS 24,25 EUR DEL 09.02.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-61.23</v>
+        <v>-24.25</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1341,18 +1341,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 86,41 EUR DEL 13.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 8,66 EUR DEL 09.02.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-86.41</v>
+        <v>-8.66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1362,18 +1362,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46067</v>
+        <v>46064</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46067</v>
+        <v>46064</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211485555 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Pagam. POS - PAGAMENTO POS 132,78 EUR DEL 11.02.2026 A (ITA) RAY-BAN LINGOTTO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>253.84</v>
+        <v>-132.78</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1383,18 +1383,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46068</v>
+        <v>46064</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4688 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 83,83 EUR DEL 11.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-77.56</v>
+        <v>-83.83</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1404,18 +1404,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 109,27 EUR DEL 15.02.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-109.27</v>
+        <v>-6.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1425,18 +1425,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46072</v>
+        <v>46067</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46073</v>
+        <v>46067</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219877801 ORD. RICARICA REVOLUT LAURA</t>
+          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>123.06</v>
+        <v>-54.05</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1446,18 +1446,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46073</v>
+        <v>46069</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46074</v>
+        <v>46070</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 37,06 EUR DEL 20.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Bonif. v/fav. - RIF:211238771 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-37.06</v>
+        <v>149.52</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1467,18 +1467,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 50,66 EUR DEL 22.02.2026 A (ITA) ZARA ITALIA SRL</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-5.85</v>
+        <v>-50.66</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1488,18 +1488,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46082</v>
+        <v>46078</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9775 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5301 UDON</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-179.22</v>
+        <v>-46.96</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
